--- a/output/pdf_financials_xlsx/MKZ.UN.xlsx
+++ b/output/pdf_financials_xlsx/MKZ.UN.xlsx
@@ -769,37 +769,37 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.017205</v>
+        <v>0.13415</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.018184</v>
+        <v>0.141876</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.016643</v>
+        <v>0.129434</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.016843</v>
+        <v>0.131963</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.016555</v>
+        <v>0.128572</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.016082</v>
+        <v>0.124767</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.014813</v>
+        <v>0.11486</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>16.124</v>
+        <v>126.364</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>15.529</v>
+        <v>119.332</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>18.609</v>
+        <v>146.68</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>22.181</v>
+        <v>174.002</v>
       </c>
     </row>
     <row r="11">
@@ -809,37 +809,37 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1.838125</v>
+        <v>1.72118</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1.805062</v>
+        <v>1.68137</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1.642756</v>
+        <v>1.529965</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1.398099</v>
+        <v>1.282979</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.332319</v>
+        <v>1.220302</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.20926</v>
+        <v>1.100575</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1.115238</v>
+        <v>1.015191</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>928.292</v>
+        <v>818.052</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>828.928</v>
+        <v>725.125</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>797.737</v>
+        <v>669.6660000000001</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>755.856</v>
+        <v>604.035</v>
       </c>
     </row>
     <row r="12">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -18539,7 +18539,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -20785,7 +20785,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -21560,7 +21560,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">
